--- a/artfynd/A 47327-2024 artfynd.xlsx
+++ b/artfynd/A 47327-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150700</v>
+        <v>121150703</v>
       </c>
       <c r="B4" t="n">
-        <v>91975</v>
+        <v>91963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714428</v>
+        <v>714466</v>
       </c>
       <c r="R4" t="n">
-        <v>7216635</v>
+        <v>7216337</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150703</v>
+        <v>121150700</v>
       </c>
       <c r="B5" t="n">
-        <v>91963</v>
+        <v>91975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>714466</v>
+        <v>714428</v>
       </c>
       <c r="R5" t="n">
-        <v>7216337</v>
+        <v>7216635</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 47327-2024 artfynd.xlsx
+++ b/artfynd/A 47327-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150701</v>
+        <v>121150700</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>714476</v>
+        <v>714428</v>
       </c>
       <c r="R2" t="n">
-        <v>7216593</v>
+        <v>7216635</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>121150702</v>
       </c>
       <c r="B3" t="n">
-        <v>91975</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150703</v>
+        <v>121150701</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91967</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714466</v>
+        <v>714476</v>
       </c>
       <c r="R4" t="n">
-        <v>7216337</v>
+        <v>7216593</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150700</v>
+        <v>121150703</v>
       </c>
       <c r="B5" t="n">
-        <v>91975</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>714428</v>
+        <v>714466</v>
       </c>
       <c r="R5" t="n">
-        <v>7216635</v>
+        <v>7216337</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 47327-2024 artfynd.xlsx
+++ b/artfynd/A 47327-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150700</v>
+        <v>121150703</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>714428</v>
+        <v>714466</v>
       </c>
       <c r="R2" t="n">
-        <v>7216635</v>
+        <v>7216337</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150702</v>
+        <v>121150701</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>91967</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>714485</v>
+        <v>714476</v>
       </c>
       <c r="R3" t="n">
-        <v>7216305</v>
+        <v>7216593</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150701</v>
+        <v>121150700</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714476</v>
+        <v>714428</v>
       </c>
       <c r="R4" t="n">
-        <v>7216593</v>
+        <v>7216635</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150703</v>
+        <v>121150702</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>714466</v>
+        <v>714485</v>
       </c>
       <c r="R5" t="n">
-        <v>7216337</v>
+        <v>7216305</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 47327-2024 artfynd.xlsx
+++ b/artfynd/A 47327-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150703</v>
+        <v>121150702</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>91997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>714466</v>
+        <v>714485</v>
       </c>
       <c r="R2" t="n">
-        <v>7216337</v>
+        <v>7216305</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>121150701</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150700</v>
+        <v>121150703</v>
       </c>
       <c r="B4" t="n">
         <v>91985</v>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714428</v>
+        <v>714466</v>
       </c>
       <c r="R4" t="n">
-        <v>7216635</v>
+        <v>7216337</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150702</v>
+        <v>121150700</v>
       </c>
       <c r="B5" t="n">
-        <v>91985</v>
+        <v>91997</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>714485</v>
+        <v>714428</v>
       </c>
       <c r="R5" t="n">
-        <v>7216305</v>
+        <v>7216635</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 47327-2024 artfynd.xlsx
+++ b/artfynd/A 47327-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150702</v>
       </c>
       <c r="B2" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150701</v>
+        <v>121150703</v>
       </c>
       <c r="B3" t="n">
-        <v>91979</v>
+        <v>91986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>714476</v>
+        <v>714466</v>
       </c>
       <c r="R3" t="n">
-        <v>7216593</v>
+        <v>7216337</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150703</v>
+        <v>121150701</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>91980</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714466</v>
+        <v>714476</v>
       </c>
       <c r="R4" t="n">
-        <v>7216337</v>
+        <v>7216593</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121150700</v>
       </c>
       <c r="B5" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 47327-2024 artfynd.xlsx
+++ b/artfynd/A 47327-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150702</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150703</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>121150701</v>
       </c>
       <c r="B4" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>121150700</v>
       </c>
       <c r="B5" t="n">
-        <v>91998</v>
+        <v>92001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 47327-2024 artfynd.xlsx
+++ b/artfynd/A 47327-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150702</v>
+        <v>121150703</v>
       </c>
       <c r="B2" t="n">
-        <v>92001</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>714485</v>
+        <v>714466</v>
       </c>
       <c r="R2" t="n">
-        <v>7216305</v>
+        <v>7216337</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150703</v>
+        <v>121150701</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>91983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>714466</v>
+        <v>714476</v>
       </c>
       <c r="R3" t="n">
-        <v>7216337</v>
+        <v>7216593</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150701</v>
+        <v>121150700</v>
       </c>
       <c r="B4" t="n">
-        <v>91983</v>
+        <v>92001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714476</v>
+        <v>714428</v>
       </c>
       <c r="R4" t="n">
-        <v>7216593</v>
+        <v>7216635</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150700</v>
+        <v>121150702</v>
       </c>
       <c r="B5" t="n">
         <v>92001</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>714428</v>
+        <v>714485</v>
       </c>
       <c r="R5" t="n">
-        <v>7216635</v>
+        <v>7216305</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 47327-2024 artfynd.xlsx
+++ b/artfynd/A 47327-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150703</v>
+        <v>121150701</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>714466</v>
+        <v>714476</v>
       </c>
       <c r="R2" t="n">
-        <v>7216337</v>
+        <v>7216593</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150701</v>
+        <v>121150703</v>
       </c>
       <c r="B3" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>714476</v>
+        <v>714466</v>
       </c>
       <c r="R3" t="n">
-        <v>7216593</v>
+        <v>7216337</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,16 +890,11 @@
         <v>121150700</v>
       </c>
       <c r="B4" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1011,16 +996,11 @@
         <v>121150702</v>
       </c>
       <c r="B5" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
